--- a/06_Office_Related/01_NSO_work/06_SL_processing/03_TN_SL_2026-27/SL 2.0/Dharmapuri.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_processing/03_TN_SL_2026-27/SL 2.0/Dharmapuri.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\TN WP 2026-27\SL 2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_processing\03_TN_SL_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B11271-5C4F-43FD-8D7E-80386B622EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71676884-0BAA-4D51-BBDA-180BD328FA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4279" yWindow="3437" windowWidth="19563" windowHeight="10161" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Working sheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="155">
   <si>
     <t>State Sample</t>
   </si>
@@ -493,6 +493,9 @@
   </si>
   <si>
     <t>COTTON (K)</t>
+  </si>
+  <si>
+    <t>Kerikodahalli</t>
   </si>
 </sst>
 </file>
@@ -808,24 +811,6 @@
     <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -852,6 +837,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -886,9 +889,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -926,9 +929,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -961,9 +964,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -996,9 +1016,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1187,104 +1224,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
     </row>
     <row r="2" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
     </row>
     <row r="3" spans="1:12" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
     </row>
     <row r="4" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
     </row>
     <row r="5" spans="1:12" ht="46.55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="51" t="s">
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51" t="s">
+      <c r="G5" s="45"/>
+      <c r="H5" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51" t="s">
+      <c r="I5" s="45"/>
+      <c r="J5" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51" t="s">
+      <c r="K5" s="45"/>
+      <c r="L5" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="35.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52"/>
-      <c r="B6" s="50"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
@@ -1312,7 +1349,7 @@
       <c r="K6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="L6" s="51"/>
+      <c r="L6" s="45"/>
     </row>
     <row r="7" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
@@ -3331,140 +3368,140 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
     </row>
     <row r="2" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
     </row>
     <row r="3" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="41" t="s">
+      <c r="Q3" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
     </row>
     <row r="4" spans="1:22" ht="40.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43" t="s">
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43" t="s">
+      <c r="G4" s="50"/>
+      <c r="H4" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43" t="s">
+      <c r="I4" s="50"/>
+      <c r="J4" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="K4" s="43"/>
-      <c r="L4" s="44" t="s">
+      <c r="K4" s="50"/>
+      <c r="L4" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44" t="s">
+      <c r="M4" s="51"/>
+      <c r="N4" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="45" t="s">
+      <c r="O4" s="51"/>
+      <c r="P4" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="Q4" s="46"/>
+      <c r="Q4" s="53"/>
       <c r="R4" s="32" t="s">
         <v>80</v>
       </c>
       <c r="S4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="T4" s="44" t="s">
+      <c r="T4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44" t="s">
+      <c r="U4" s="51"/>
+      <c r="V4" s="51" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="27.2" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
       <c r="C5" s="11" t="s">
         <v>20</v>
       </c>
@@ -3522,11 +3559,11 @@
       <c r="U5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="V5" s="44"/>
+      <c r="V5" s="51"/>
     </row>
     <row r="6" spans="1:22" s="13" customFormat="1" ht="25.85" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="12" t="s">
         <v>25</v>
       </c>
@@ -3587,30 +3624,30 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="43"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="50"/>
     </row>
     <row r="8" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
@@ -3680,9 +3717,11 @@
     </row>
     <row r="10" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>154</v>
+      </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -3743,30 +3782,30 @@
       <c r="V11" s="11"/>
     </row>
     <row r="12" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
     </row>
     <row r="13" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
@@ -4500,6 +4539,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:V3"/>
     <mergeCell ref="A7:V7"/>
     <mergeCell ref="A12:V12"/>
     <mergeCell ref="J4:K4"/>
@@ -4513,11 +4557,6 @@
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:V3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="K15" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -6058,134 +6097,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
     </row>
     <row r="2" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
     </row>
     <row r="3" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="41" t="s">
+      <c r="Q3" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
     </row>
     <row r="4" spans="1:21" ht="40.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43" t="s">
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43" t="s">
+      <c r="G4" s="50"/>
+      <c r="H4" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43" t="s">
+      <c r="I4" s="50"/>
+      <c r="J4" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="43"/>
-      <c r="L4" s="44" t="s">
+      <c r="K4" s="50"/>
+      <c r="L4" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44" t="s">
+      <c r="M4" s="51"/>
+      <c r="N4" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="45" t="s">
+      <c r="O4" s="51"/>
+      <c r="P4" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="Q4" s="46"/>
+      <c r="Q4" s="53"/>
       <c r="R4" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="S4" s="44" t="s">
+      <c r="S4" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44" t="s">
+      <c r="T4" s="51"/>
+      <c r="U4" s="51" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="27.2" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
       <c r="C5" s="11" t="s">
         <v>20</v>
       </c>
@@ -6240,11 +6279,11 @@
       <c r="T5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="U5" s="44"/>
+      <c r="U5" s="51"/>
     </row>
     <row r="6" spans="1:21" s="13" customFormat="1" ht="38.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="12" t="s">
         <v>25</v>
       </c>
@@ -6581,29 +6620,29 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="50"/>
+      <c r="L16" s="50"/>
+      <c r="M16" s="50"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="50"/>
+      <c r="S16" s="50"/>
+      <c r="T16" s="50"/>
+      <c r="U16" s="50"/>
     </row>
     <row r="17" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
@@ -6860,6 +6899,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:U3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
@@ -6876,11 +6920,6 @@
     <mergeCell ref="U4:U5"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="O25:R25"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:U3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="K8" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
